--- a/src/test/resources/TestData/data.xlsx
+++ b/src/test/resources/TestData/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E2C5B3-BD97-46AB-BA66-32A68D4FBEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CD67BB-9841-4494-80E8-B19918543225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10032" uniqueCount="3476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10036" uniqueCount="3476">
   <si>
     <t>TCName</t>
   </si>
@@ -8372,9 +8372,6 @@
     <t>Verification of Stop Functionality of Edge Groups</t>
   </si>
   <si>
-    <t>PermianBasin1</t>
-  </si>
-  <si>
     <t>TC143_Verify Edit functionality of Edge Group</t>
   </si>
   <si>
@@ -10653,6 +10650,9 @@
   </si>
   <si>
     <t>PermianBasin</t>
+  </si>
+  <si>
+    <t>TC142_Verify Edit functionality for edge Group Name under Registration Section for upload</t>
   </si>
 </sst>
 </file>
@@ -12002,7 +12002,7 @@
         <v>27</v>
       </c>
       <c r="D21" s="72" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E21" s="72" t="s">
         <v>2473</v>
@@ -12019,10 +12019,10 @@
         <v>27</v>
       </c>
       <c r="D22" s="72" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E22" s="72" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="76" customFormat="1" ht="39" x14ac:dyDescent="0.35">
@@ -12958,7 +12958,7 @@
     </row>
     <row r="20" spans="1:27" s="10" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>884</v>
@@ -12974,11 +12974,11 @@
       </c>
       <c r="M20" s="3" t="str">
         <f ca="1">"Cygnet_Hardware"&amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>Cygnet_Hardware12082024163244</v>
+        <v>Cygnet_Hardware12082024222959</v>
       </c>
       <c r="N20" s="10" t="str">
         <f ca="1">"Cygnet_Hardware"&amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>Cygnet_Hardware12082024163244</v>
+        <v>Cygnet_Hardware12082024222959</v>
       </c>
       <c r="O20" s="10" t="s">
         <v>887</v>
@@ -12999,7 +12999,7 @@
     </row>
     <row r="21" spans="1:27" s="10" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>885</v>
@@ -13047,7 +13047,7 @@
     </row>
     <row r="22" spans="1:27" s="10" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>886</v>
@@ -13069,7 +13069,7 @@
     </row>
     <row r="23" spans="1:27" s="10" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>1013</v>
@@ -13195,7 +13195,7 @@
     </row>
     <row r="29" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="B29" s="48" t="s">
         <v>1805</v>
@@ -13213,10 +13213,10 @@
     </row>
     <row r="30" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>27</v>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="31" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>27</v>
@@ -13249,10 +13249,10 @@
     </row>
     <row r="32" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>27</v>
@@ -13267,10 +13267,10 @@
     </row>
     <row r="33" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>27</v>
@@ -13285,10 +13285,10 @@
     </row>
     <row r="34" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>27</v>
@@ -13303,10 +13303,10 @@
     </row>
     <row r="35" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>27</v>
@@ -13321,10 +13321,10 @@
     </row>
     <row r="36" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>27</v>
@@ -13339,10 +13339,10 @@
     </row>
     <row r="37" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>27</v>
@@ -13357,10 +13357,10 @@
     </row>
     <row r="38" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>27</v>
@@ -13375,10 +13375,10 @@
     </row>
     <row r="39" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>27</v>
@@ -13393,10 +13393,10 @@
     </row>
     <row r="40" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>27</v>
@@ -13411,10 +13411,10 @@
     </row>
     <row r="41" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>27</v>
@@ -13429,10 +13429,10 @@
     </row>
     <row r="42" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>27</v>
@@ -13447,7 +13447,7 @@
     </row>
     <row r="43" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="B43" s="49" t="s">
         <v>2509</v>
@@ -13465,7 +13465,7 @@
     </row>
     <row r="44" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="B44" s="49" t="s">
         <v>1816</v>
@@ -13483,7 +13483,7 @@
     </row>
     <row r="45" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="B45" s="49" t="s">
         <v>1795</v>
@@ -13501,7 +13501,7 @@
     </row>
     <row r="46" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="B46" s="49" t="s">
         <v>1924</v>
@@ -13519,10 +13519,10 @@
     </row>
     <row r="47" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>27</v>
@@ -13537,7 +13537,7 @@
     </row>
     <row r="48" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="B48" s="49" t="s">
         <v>2024</v>
@@ -13555,7 +13555,7 @@
     </row>
     <row r="49" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B49" s="49" t="s">
         <v>1784</v>
@@ -13573,7 +13573,7 @@
     </row>
     <row r="50" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B50" s="49" t="s">
         <v>1785</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="51" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B51" s="49" t="s">
         <v>1786</v>
@@ -13607,7 +13607,7 @@
     </row>
     <row r="52" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B52" s="49" t="s">
         <v>1787</v>
@@ -13624,10 +13624,10 @@
     </row>
     <row r="53" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>27</v>
@@ -13641,10 +13641,10 @@
     </row>
     <row r="54" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>27</v>
@@ -13658,10 +13658,10 @@
     </row>
     <row r="55" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>27</v>
@@ -13675,10 +13675,10 @@
     </row>
     <row r="56" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>27</v>
@@ -13692,10 +13692,10 @@
     </row>
     <row r="57" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>27</v>
@@ -13709,10 +13709,10 @@
     </row>
     <row r="58" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>27</v>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="59" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>27</v>
@@ -13743,7 +13743,7 @@
     </row>
     <row r="60" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B60" s="49" t="s">
         <v>1795</v>
@@ -13760,7 +13760,7 @@
     </row>
     <row r="61" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B61" s="49" t="s">
         <v>1924</v>
@@ -13777,10 +13777,10 @@
     </row>
     <row r="62" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B62" s="49" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="C62" s="14" t="s">
         <v>27</v>
@@ -13794,10 +13794,10 @@
     </row>
     <row r="63" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>27</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="64" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>27</v>
@@ -13828,10 +13828,10 @@
     </row>
     <row r="65" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="B65" s="49" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>27</v>
@@ -13845,10 +13845,10 @@
     </row>
     <row r="66" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="B66" s="49" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="C66" s="14" t="s">
         <v>27</v>
@@ -13862,10 +13862,10 @@
     </row>
     <row r="67" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>27</v>
@@ -13879,7 +13879,7 @@
     </row>
     <row r="68" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="B68" s="49" t="s">
         <v>2517</v>
@@ -13896,7 +13896,7 @@
     </row>
     <row r="69" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="B69" s="49" t="s">
         <v>2155</v>
@@ -13916,7 +13916,7 @@
     </row>
     <row r="70" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="B70" s="49" t="s">
         <v>2035</v>
@@ -13936,7 +13936,7 @@
     </row>
     <row r="71" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="B71" s="49" t="s">
         <v>2036</v>
@@ -13956,7 +13956,7 @@
     </row>
     <row r="72" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="B72" s="49" t="s">
         <v>2037</v>
@@ -13976,10 +13976,10 @@
     </row>
     <row r="73" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="B73" s="49" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>27</v>
@@ -13993,10 +13993,10 @@
     </row>
     <row r="74" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="B74" s="49" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="C74" s="14" t="s">
         <v>27</v>
@@ -14010,10 +14010,10 @@
     </row>
     <row r="75" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="B75" s="49" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>27</v>
@@ -14027,10 +14027,10 @@
     </row>
     <row r="76" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B76" s="49" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="C76" s="14" t="s">
         <v>27</v>
@@ -14044,10 +14044,10 @@
     </row>
     <row r="77" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="B77" s="49" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="C77" s="14" t="s">
         <v>27</v>
@@ -14061,10 +14061,10 @@
     </row>
     <row r="78" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="B78" s="49" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="C78" s="14" t="s">
         <v>27</v>
@@ -14078,7 +14078,7 @@
     </row>
     <row r="79" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="B79" s="49" t="s">
         <v>2042</v>
@@ -14095,7 +14095,7 @@
     </row>
     <row r="80" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="B80" s="49" t="s">
         <v>2043</v>
@@ -14112,7 +14112,7 @@
     </row>
     <row r="81" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B81" s="49" t="s">
         <v>2044</v>
@@ -14129,10 +14129,10 @@
     </row>
     <row r="82" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="B82" s="49" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>27</v>
@@ -14146,10 +14146,10 @@
     </row>
     <row r="83" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="B83" s="49" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>27</v>
@@ -14163,10 +14163,10 @@
     </row>
     <row r="84" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="B84" s="49" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>27</v>
@@ -14180,10 +14180,10 @@
     </row>
     <row r="85" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="B85" s="49" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>27</v>
@@ -14197,10 +14197,10 @@
     </row>
     <row r="86" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B86" s="49" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>27</v>
@@ -14214,10 +14214,10 @@
     </row>
     <row r="87" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="B87" s="49" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>27</v>
@@ -14231,10 +14231,10 @@
     </row>
     <row r="88" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="B88" s="49" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="C88" s="14" t="s">
         <v>27</v>
@@ -14248,10 +14248,10 @@
     </row>
     <row r="89" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="B89" s="49" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="C89" s="14" t="s">
         <v>27</v>
@@ -14265,10 +14265,10 @@
     </row>
     <row r="90" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="B90" s="49" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>27</v>
@@ -14282,10 +14282,10 @@
     </row>
     <row r="91" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="B91" s="49" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>27</v>
@@ -14299,10 +14299,10 @@
     </row>
     <row r="92" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B92" s="49" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>27</v>
@@ -14316,10 +14316,10 @@
     </row>
     <row r="93" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="B93" s="49" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>27</v>
@@ -14333,10 +14333,10 @@
     </row>
     <row r="94" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="B94" s="49" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>27</v>
@@ -14350,10 +14350,10 @@
     </row>
     <row r="95" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="B95" s="49" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>27</v>
@@ -14367,7 +14367,7 @@
     </row>
     <row r="96" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="B96" s="49" t="s">
         <v>2056</v>
@@ -14384,7 +14384,7 @@
     </row>
     <row r="97" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="B97" s="49" t="s">
         <v>1827</v>
@@ -14401,7 +14401,7 @@
     </row>
     <row r="98" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="B98" s="49" t="s">
         <v>1828</v>
@@ -14418,7 +14418,7 @@
     </row>
     <row r="99" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="B99" s="49" t="s">
         <v>1829</v>
@@ -14435,7 +14435,7 @@
     </row>
     <row r="100" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="B100" s="49" t="s">
         <v>2060</v>
@@ -14452,7 +14452,7 @@
     </row>
     <row r="101" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="B101" s="49" t="s">
         <v>2156</v>
@@ -14469,7 +14469,7 @@
     </row>
     <row r="102" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="B102" s="49" t="s">
         <v>1827</v>
@@ -14486,7 +14486,7 @@
     </row>
     <row r="103" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="B103" s="49" t="s">
         <v>1828</v>
@@ -14503,7 +14503,7 @@
     </row>
     <row r="104" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="B104" s="49" t="s">
         <v>1829</v>
@@ -14520,7 +14520,7 @@
     </row>
     <row r="105" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="B105" s="49" t="s">
         <v>2060</v>
@@ -14537,7 +14537,7 @@
     </row>
     <row r="106" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="B106" s="49" t="s">
         <v>2156</v>
@@ -14554,7 +14554,7 @@
     </row>
     <row r="107" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="B107" s="49" t="s">
         <v>2012</v>
@@ -14571,7 +14571,7 @@
     </row>
     <row r="108" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="B108" s="49" t="s">
         <v>2013</v>
@@ -14588,10 +14588,10 @@
     </row>
     <row r="109" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="B109" s="48" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>27</v>
@@ -14605,7 +14605,7 @@
     </row>
     <row r="110" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B110" s="48" t="s">
         <v>1832</v>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="I61" s="8" t="str">
         <f ca="1">"Volume123" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>Volume12312082024163244</v>
+        <v>Volume12312082024222959</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>1775</v>
@@ -16172,7 +16172,7 @@
       </c>
       <c r="T65" s="34" t="str">
         <f ca="1">"VolumeTest" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>VolumeTest12082024163244</v>
+        <v>VolumeTest12082024222959</v>
       </c>
       <c r="U65" s="8" t="s">
         <v>1775</v>
@@ -16183,7 +16183,7 @@
     </row>
     <row r="66" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="25" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="14" t="s">
@@ -16199,7 +16199,7 @@
     </row>
     <row r="67" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A67" s="25" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="14" t="s">
@@ -16215,7 +16215,7 @@
     </row>
     <row r="68" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A68" s="25" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="14" t="s">
@@ -16231,7 +16231,7 @@
     </row>
     <row r="69" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A69" s="25" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="14" t="s">
@@ -16247,7 +16247,7 @@
     </row>
     <row r="70" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A70" s="25" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="14" t="s">
@@ -16263,7 +16263,7 @@
     </row>
     <row r="71" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="25" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="14" t="s">
@@ -16279,7 +16279,7 @@
     </row>
     <row r="72" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="25" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="14" t="s">
@@ -16295,7 +16295,7 @@
     </row>
     <row r="73" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="25" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="14" t="s">
@@ -16311,7 +16311,7 @@
     </row>
     <row r="74" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="25" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="14" t="s">
@@ -16327,7 +16327,7 @@
     </row>
     <row r="75" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="25" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="14" t="s">
@@ -16343,30 +16343,30 @@
     </row>
     <row r="76" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="35" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B76" s="117" t="s">
         <v>2857</v>
       </c>
-      <c r="B76" s="117" t="s">
+      <c r="C76" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D76" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F76" s="8" t="s">
         <v>2858</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D76" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E76" s="26" t="s">
-        <v>2473</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>2859</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="B77" s="117" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="C77" s="14" t="s">
         <v>27</v>
@@ -16380,10 +16380,10 @@
     </row>
     <row r="78" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="35" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="B78" s="117" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="C78" s="14" t="s">
         <v>27</v>
@@ -16397,7 +16397,7 @@
     </row>
     <row r="79" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="35" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="B79" s="117" t="s">
         <v>2509</v>
@@ -16414,7 +16414,7 @@
     </row>
     <row r="80" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="35" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="B80" s="117" t="s">
         <v>1816</v>
@@ -16431,7 +16431,7 @@
     </row>
     <row r="81" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="35" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="B81" s="117" t="s">
         <v>1795</v>
@@ -16448,7 +16448,7 @@
     </row>
     <row r="82" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="35" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="B82" s="117" t="s">
         <v>1924</v>
@@ -16465,10 +16465,10 @@
     </row>
     <row r="83" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="35" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="B83" s="117" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>27</v>
@@ -16482,7 +16482,7 @@
     </row>
     <row r="84" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" s="35" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B84" s="117" t="s">
         <v>2024</v>
@@ -16499,7 +16499,7 @@
     </row>
     <row r="85" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="35" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="B85" s="117" t="s">
         <v>1784</v>
@@ -16516,7 +16516,7 @@
     </row>
     <row r="86" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="35" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="B86" s="117" t="s">
         <v>1785</v>
@@ -16533,7 +16533,7 @@
     </row>
     <row r="87" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="35" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="B87" s="117" t="s">
         <v>1786</v>
@@ -16550,7 +16550,7 @@
     </row>
     <row r="88" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="35" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="B88" s="117" t="s">
         <v>1787</v>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="89" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="35" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="C89" s="14" t="s">
         <v>27</v>
@@ -16584,10 +16584,10 @@
     </row>
     <row r="90" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="35" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="B90" s="117" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>27</v>
@@ -16601,10 +16601,10 @@
     </row>
     <row r="91" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="35" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="B91" s="117" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>27</v>
@@ -16618,10 +16618,10 @@
     </row>
     <row r="92" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="35" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="B92" s="117" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>27</v>
@@ -16635,7 +16635,7 @@
     </row>
     <row r="93" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="35" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="B93" s="117" t="s">
         <v>1795</v>
@@ -16652,7 +16652,7 @@
     </row>
     <row r="94" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="35" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="B94" s="117" t="s">
         <v>1924</v>
@@ -16669,10 +16669,10 @@
     </row>
     <row r="95" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A95" s="35" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="B95" s="117" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>27</v>
@@ -16686,10 +16686,10 @@
     </row>
     <row r="96" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="35" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="B96" s="117" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>27</v>
@@ -16703,10 +16703,10 @@
     </row>
     <row r="97" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="35" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="B97" s="117" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>27</v>
@@ -16720,7 +16720,7 @@
     </row>
     <row r="98" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="35" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="B98" s="117" t="s">
         <v>2517</v>
@@ -16737,7 +16737,7 @@
     </row>
     <row r="99" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="35" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="B99" s="117" t="s">
         <v>2155</v>
@@ -16757,7 +16757,7 @@
     </row>
     <row r="100" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="35" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="B100" s="117" t="s">
         <v>2035</v>
@@ -16777,7 +16777,7 @@
     </row>
     <row r="101" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="35" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="B101" s="117" t="s">
         <v>2036</v>
@@ -16797,7 +16797,7 @@
     </row>
     <row r="102" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="35" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="B102" s="117" t="s">
         <v>2037</v>
@@ -16817,10 +16817,10 @@
     </row>
     <row r="103" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="35" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="B103" s="117" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="C103" s="14" t="s">
         <v>27</v>
@@ -16834,10 +16834,10 @@
     </row>
     <row r="104" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="35" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="B104" s="117" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="C104" s="14" t="s">
         <v>27</v>
@@ -16851,10 +16851,10 @@
     </row>
     <row r="105" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="35" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="B105" s="117" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="C105" s="14" t="s">
         <v>27</v>
@@ -16868,7 +16868,7 @@
     </row>
     <row r="106" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="35" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B106" s="117" t="s">
         <v>2042</v>
@@ -16885,7 +16885,7 @@
     </row>
     <row r="107" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="35" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="B107" s="117" t="s">
         <v>2043</v>
@@ -16902,10 +16902,10 @@
     </row>
     <row r="108" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="35" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="B108" s="117" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>27</v>
@@ -16919,10 +16919,10 @@
     </row>
     <row r="109" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="35" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="B109" s="117" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>27</v>
@@ -16939,10 +16939,10 @@
     </row>
     <row r="110" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="35" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="B110" s="117" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="C110" s="14" t="s">
         <v>27</v>
@@ -16959,10 +16959,10 @@
     </row>
     <row r="111" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" s="35" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="B111" s="117" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="C111" s="14" t="s">
         <v>27</v>
@@ -16979,10 +16979,10 @@
     </row>
     <row r="112" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A112" s="35" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="B112" s="117" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C112" s="14" t="s">
         <v>27</v>
@@ -16996,10 +16996,10 @@
     </row>
     <row r="113" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="35" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="B113" s="117" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>27</v>
@@ -17013,10 +17013,10 @@
     </row>
     <row r="114" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" s="35" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="B114" s="117" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="C114" s="14" t="s">
         <v>27</v>
@@ -17030,10 +17030,10 @@
     </row>
     <row r="115" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A115" s="35" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="B115" s="117" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="C115" s="14" t="s">
         <v>27</v>
@@ -17047,10 +17047,10 @@
     </row>
     <row r="116" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="35" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="B116" s="117" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="C116" s="14" t="s">
         <v>27</v>
@@ -17064,10 +17064,10 @@
     </row>
     <row r="117" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" s="35" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="B117" s="117" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="C117" s="14" t="s">
         <v>27</v>
@@ -17081,10 +17081,10 @@
     </row>
     <row r="118" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A118" s="35" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="B118" s="117" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="C118" s="14" t="s">
         <v>27</v>
@@ -17098,10 +17098,10 @@
     </row>
     <row r="119" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A119" s="35" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="B119" s="117" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="C119" s="14" t="s">
         <v>27</v>
@@ -17115,10 +17115,10 @@
     </row>
     <row r="120" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A120" s="119" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="B120" s="118" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="C120" s="14" t="s">
         <v>27</v>
@@ -17132,7 +17132,7 @@
     </row>
     <row r="121" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="119" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B121" s="117" t="s">
         <v>2056</v>
@@ -17149,7 +17149,7 @@
     </row>
     <row r="122" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="119" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="B122" s="117" t="s">
         <v>1827</v>
@@ -17166,7 +17166,7 @@
     </row>
     <row r="123" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="119" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B123" s="117" t="s">
         <v>1828</v>
@@ -17183,7 +17183,7 @@
     </row>
     <row r="124" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="119" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="B124" s="117" t="s">
         <v>1829</v>
@@ -17200,7 +17200,7 @@
     </row>
     <row r="125" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="119" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="B125" s="117" t="s">
         <v>2060</v>
@@ -17217,7 +17217,7 @@
     </row>
     <row r="126" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="119" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="B126" s="117" t="s">
         <v>2156</v>
@@ -17234,7 +17234,7 @@
     </row>
     <row r="127" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="119" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="B127" s="117" t="s">
         <v>1827</v>
@@ -17251,7 +17251,7 @@
     </row>
     <row r="128" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="119" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="B128" s="117" t="s">
         <v>1828</v>
@@ -17268,7 +17268,7 @@
     </row>
     <row r="129" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="119" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="B129" s="117" t="s">
         <v>1829</v>
@@ -17285,7 +17285,7 @@
     </row>
     <row r="130" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="35" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="B130" s="117" t="s">
         <v>2060</v>
@@ -17302,7 +17302,7 @@
     </row>
     <row r="131" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="35" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="B131" s="117" t="s">
         <v>2156</v>
@@ -17319,10 +17319,10 @@
     </row>
     <row r="132" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="35" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="B132" s="117" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="C132" s="14" t="s">
         <v>27</v>
@@ -17336,7 +17336,7 @@
     </row>
     <row r="133" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="35" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="B133" s="117" t="s">
         <v>2013</v>
@@ -17353,10 +17353,10 @@
     </row>
     <row r="134" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="35" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="B134" s="118" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="C134" s="14" t="s">
         <v>27</v>
@@ -17370,7 +17370,7 @@
     </row>
     <row r="135" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="35" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="B135" s="118" t="s">
         <v>1832</v>
@@ -17387,7 +17387,7 @@
     </row>
     <row r="136" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="35" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="B136" s="117" t="s">
         <v>2061</v>
@@ -17404,7 +17404,7 @@
     </row>
     <row r="137" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="35" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="B137" s="117" t="s">
         <v>2062</v>
@@ -17421,10 +17421,10 @@
     </row>
     <row r="138" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A138" s="35" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="B138" s="117" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="C138" s="14" t="s">
         <v>27</v>
@@ -17438,10 +17438,10 @@
     </row>
     <row r="139" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A139" s="35" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="B139" s="117" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="C139" s="14" t="s">
         <v>27</v>
@@ -17455,10 +17455,10 @@
     </row>
     <row r="140" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A140" s="35" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B140" s="117" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="C140" s="14" t="s">
         <v>27</v>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="141" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A141" s="35" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="B141" s="117" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="C141" s="14" t="s">
         <v>27</v>
@@ -17489,10 +17489,10 @@
     </row>
     <row r="142" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A142" s="35" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="B142" s="117" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="C142" s="14" t="s">
         <v>27</v>
@@ -17506,10 +17506,10 @@
     </row>
     <row r="143" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A143" s="35" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="B143" s="117" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="C143" s="14" t="s">
         <v>27</v>
@@ -17523,10 +17523,10 @@
     </row>
     <row r="144" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A144" s="35" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B144" s="117" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>27</v>
@@ -17540,10 +17540,10 @@
     </row>
     <row r="145" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A145" s="35" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B145" s="117" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="C145" s="14" t="s">
         <v>27</v>
@@ -17557,10 +17557,10 @@
     </row>
     <row r="146" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A146" s="35" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B146" s="117" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="C146" s="14" t="s">
         <v>27</v>
@@ -17574,10 +17574,10 @@
     </row>
     <row r="147" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A147" s="35" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B147" s="117" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="C147" s="14" t="s">
         <v>27</v>
@@ -17591,10 +17591,10 @@
     </row>
     <row r="148" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A148" s="35" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="B148" s="117" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="C148" s="14" t="s">
         <v>27</v>
@@ -17829,7 +17829,7 @@
         <v>2473</v>
       </c>
       <c r="G6" s="122" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="26" x14ac:dyDescent="0.35">
@@ -18902,7 +18902,7 @@
     </row>
     <row r="36" spans="1:13" ht="26" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>1817</v>
@@ -18923,7 +18923,7 @@
     </row>
     <row r="37" spans="1:13" ht="26" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>1818</v>
@@ -18965,7 +18965,7 @@
     </row>
     <row r="39" spans="1:13" ht="26" x14ac:dyDescent="0.35">
       <c r="A39" s="15" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>1820</v>
@@ -19256,7 +19256,7 @@
     </row>
     <row r="53" spans="1:13" ht="26" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>1830</v>
@@ -19276,7 +19276,7 @@
     </row>
     <row r="54" spans="1:13" ht="39" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>1831</v>
@@ -19296,7 +19296,7 @@
     </row>
     <row r="55" spans="1:13" ht="26" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>1832</v>
@@ -19650,7 +19650,7 @@
       </c>
       <c r="J12" s="8" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>1131</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="J13" s="8" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>1131</v>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="J16" s="8" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>559</v>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="J17" s="8" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>559</v>
@@ -19839,7 +19839,7 @@
       </c>
       <c r="J18" s="8" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>559</v>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="J19" s="8" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>559</v>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="J20" s="8" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>559</v>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="J21" s="31" t="str">
         <f ca="1">"WELL" &amp; TEXT(NOW(),"yyyyMMddhhmmss")</f>
-        <v>WELL20240812163244</v>
+        <v>WELL20240812222959</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>559</v>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="J22" s="31" t="str">
         <f ca="1">"WELL" &amp; TEXT(NOW(),"yyyyMMddhhmmss")</f>
-        <v>WELL20240812163244</v>
+        <v>WELL20240812222959</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>559</v>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="F59" s="21" t="str">
         <f ca="1">"WELL56" &amp; TEXT(NOW(),"yyyyMMddhhmmss")</f>
-        <v>WELL5620240812163244</v>
+        <v>WELL5620240812222959</v>
       </c>
       <c r="G59" s="10">
         <v>12345678</v>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">"TestSuperAdmin" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>TestSuperAdmin12082024163244</v>
+        <v>TestSuperAdmin12082024222959</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>875</v>
@@ -22277,7 +22277,7 @@
         <v>1042</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>27</v>
@@ -22291,10 +22291,10 @@
     </row>
     <row r="12" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>27</v>
@@ -22311,10 +22311,10 @@
     </row>
     <row r="13" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>27</v>
@@ -22328,10 +22328,10 @@
     </row>
     <row r="14" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="C14" s="35" t="s">
         <v>27</v>
@@ -22345,10 +22345,10 @@
     </row>
     <row r="15" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="C15" s="35" t="s">
         <v>27</v>
@@ -22362,7 +22362,7 @@
     </row>
     <row r="16" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="B16" s="48" t="s">
         <v>1804</v>
@@ -22379,7 +22379,7 @@
     </row>
     <row r="17" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B17" s="48" t="s">
         <v>1805</v>
@@ -22396,10 +22396,10 @@
     </row>
     <row r="18" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>27</v>
@@ -22434,10 +22434,10 @@
     </row>
     <row r="19" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="C19" s="35" t="s">
         <v>27</v>
@@ -22466,10 +22466,10 @@
     </row>
     <row r="20" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="C20" s="35" t="s">
         <v>27</v>
@@ -22483,10 +22483,10 @@
     </row>
     <row r="21" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="C21" s="35" t="s">
         <v>27</v>
@@ -22500,10 +22500,10 @@
     </row>
     <row r="22" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="C22" s="35" t="s">
         <v>27</v>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="23" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="C23" s="35" t="s">
         <v>27</v>
@@ -22536,7 +22536,7 @@
     </row>
     <row r="24" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="B24" s="49" t="s">
         <v>2509</v>
@@ -22554,7 +22554,7 @@
     </row>
     <row r="25" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="B25" s="49" t="s">
         <v>1816</v>
@@ -22572,7 +22572,7 @@
     </row>
     <row r="26" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="B26" s="49" t="s">
         <v>1795</v>
@@ -22590,7 +22590,7 @@
     </row>
     <row r="27" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="B27" s="49" t="s">
         <v>1924</v>
@@ -22608,10 +22608,10 @@
     </row>
     <row r="28" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>27</v>
@@ -22626,7 +22626,7 @@
     </row>
     <row r="29" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="B29" s="49" t="s">
         <v>2024</v>
@@ -22644,7 +22644,7 @@
     </row>
     <row r="30" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="B30" s="49" t="s">
         <v>1784</v>
@@ -22662,7 +22662,7 @@
     </row>
     <row r="31" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="B31" s="49" t="s">
         <v>1785</v>
@@ -22680,7 +22680,7 @@
     </row>
     <row r="32" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="B32" s="49" t="s">
         <v>1786</v>
@@ -22698,7 +22698,7 @@
     </row>
     <row r="33" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="B33" s="49" t="s">
         <v>1787</v>
@@ -22716,10 +22716,10 @@
     </row>
     <row r="34" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C34" s="35" t="s">
         <v>27</v>
@@ -22734,10 +22734,10 @@
     </row>
     <row r="35" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="C35" s="35" t="s">
         <v>27</v>
@@ -22752,10 +22752,10 @@
     </row>
     <row r="36" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="C36" s="35" t="s">
         <v>27</v>
@@ -22770,10 +22770,10 @@
     </row>
     <row r="37" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C37" s="35" t="s">
         <v>27</v>
@@ -22788,10 +22788,10 @@
     </row>
     <row r="38" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B38" s="47" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="C38" s="35" t="s">
         <v>27</v>
@@ -22806,7 +22806,7 @@
     </row>
     <row r="39" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B39" s="49" t="s">
         <v>1924</v>
@@ -22824,10 +22824,10 @@
     </row>
     <row r="40" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="C40" s="35" t="s">
         <v>27</v>
@@ -22842,10 +22842,10 @@
     </row>
     <row r="41" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="C41" s="35" t="s">
         <v>27</v>
@@ -22860,10 +22860,10 @@
     </row>
     <row r="42" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="C42" s="35" t="s">
         <v>27</v>
@@ -22896,7 +22896,7 @@
     </row>
     <row r="44" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B44" s="49" t="s">
         <v>2155</v>
@@ -22914,7 +22914,7 @@
     </row>
     <row r="45" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B45" s="49" t="s">
         <v>2035</v>
@@ -22935,7 +22935,7 @@
     </row>
     <row r="46" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B46" s="49" t="s">
         <v>2036</v>
@@ -22956,7 +22956,7 @@
     </row>
     <row r="47" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B47" s="49" t="s">
         <v>2037</v>
@@ -22977,10 +22977,10 @@
     </row>
     <row r="48" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="C48" s="35" t="s">
         <v>27</v>
@@ -22995,10 +22995,10 @@
     </row>
     <row r="49" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="C49" s="35" t="s">
         <v>27</v>
@@ -23013,10 +23013,10 @@
     </row>
     <row r="50" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="C50" s="35" t="s">
         <v>27</v>
@@ -23030,7 +23030,7 @@
     </row>
     <row r="51" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B51" s="49" t="s">
         <v>2042</v>
@@ -23047,10 +23047,10 @@
     </row>
     <row r="52" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="C52" s="35" t="s">
         <v>27</v>
@@ -23064,10 +23064,10 @@
     </row>
     <row r="53" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B53" s="116" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="C53" s="35" t="s">
         <v>27</v>
@@ -23081,10 +23081,10 @@
     </row>
     <row r="54" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B54" s="116" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="C54" s="35" t="s">
         <v>27</v>
@@ -23098,10 +23098,10 @@
     </row>
     <row r="55" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B55" s="116" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="C55" s="35" t="s">
         <v>27</v>
@@ -23115,10 +23115,10 @@
     </row>
     <row r="56" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B56" s="116" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="C56" s="35" t="s">
         <v>27</v>
@@ -23132,10 +23132,10 @@
     </row>
     <row r="57" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="B57" s="116" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="C57" s="35" t="s">
         <v>27</v>
@@ -23149,10 +23149,10 @@
     </row>
     <row r="58" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="B58" s="116" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="C58" s="35" t="s">
         <v>27</v>
@@ -23166,10 +23166,10 @@
     </row>
     <row r="59" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="C59" s="35" t="s">
         <v>27</v>
@@ -23183,10 +23183,10 @@
     </row>
     <row r="60" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="C60" s="35" t="s">
         <v>27</v>
@@ -23200,10 +23200,10 @@
     </row>
     <row r="61" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="C61" s="35" t="s">
         <v>27</v>
@@ -23217,10 +23217,10 @@
     </row>
     <row r="62" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="B62" s="49" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="C62" s="35" t="s">
         <v>27</v>
@@ -23234,10 +23234,10 @@
     </row>
     <row r="63" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="C63" s="35" t="s">
         <v>27</v>
@@ -23251,10 +23251,10 @@
     </row>
     <row r="64" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="C64" s="35" t="s">
         <v>27</v>
@@ -23268,7 +23268,7 @@
     </row>
     <row r="65" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B65" s="49" t="s">
         <v>1044</v>
@@ -23285,7 +23285,7 @@
     </row>
     <row r="66" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="B66" s="49" t="s">
         <v>2056</v>
@@ -23302,7 +23302,7 @@
     </row>
     <row r="67" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="B67" s="49" t="s">
         <v>1827</v>
@@ -23319,7 +23319,7 @@
     </row>
     <row r="68" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="B68" s="49" t="s">
         <v>1828</v>
@@ -23336,7 +23336,7 @@
     </row>
     <row r="69" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="B69" s="49" t="s">
         <v>1829</v>
@@ -23353,7 +23353,7 @@
     </row>
     <row r="70" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="B70" s="49" t="s">
         <v>2060</v>
@@ -23370,7 +23370,7 @@
     </row>
     <row r="71" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="B71" s="49" t="s">
         <v>2156</v>
@@ -23387,7 +23387,7 @@
     </row>
     <row r="72" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="B72" s="49" t="s">
         <v>1827</v>
@@ -23404,7 +23404,7 @@
     </row>
     <row r="73" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="B73" s="49" t="s">
         <v>1828</v>
@@ -23421,10 +23421,10 @@
     </row>
     <row r="74" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="B74" s="49" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="C74" s="35" t="s">
         <v>27</v>
@@ -23438,7 +23438,7 @@
     </row>
     <row r="75" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B75" s="49" t="s">
         <v>2060</v>
@@ -23455,7 +23455,7 @@
     </row>
     <row r="76" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="B76" s="49" t="s">
         <v>2156</v>
@@ -23472,10 +23472,10 @@
     </row>
     <row r="77" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="B77" s="49" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C77" s="35" t="s">
         <v>27</v>
@@ -23489,10 +23489,10 @@
     </row>
     <row r="78" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="B78" s="49" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="C78" s="35" t="s">
         <v>27</v>
@@ -23506,10 +23506,10 @@
     </row>
     <row r="79" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="B79" s="48" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="C79" s="35" t="s">
         <v>27</v>
@@ -23523,7 +23523,7 @@
     </row>
     <row r="80" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B80" s="48" t="s">
         <v>1832</v>
@@ -23540,7 +23540,7 @@
     </row>
     <row r="81" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="B81" s="49" t="s">
         <v>2061</v>
@@ -23557,7 +23557,7 @@
     </row>
     <row r="82" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="B82" s="49" t="s">
         <v>2062</v>
@@ -23574,10 +23574,10 @@
     </row>
     <row r="83" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="B83" s="49" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="C83" s="35" t="s">
         <v>27</v>
@@ -23591,10 +23591,10 @@
     </row>
     <row r="84" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="B84" s="49" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="C84" s="35" t="s">
         <v>27</v>
@@ -23608,10 +23608,10 @@
     </row>
     <row r="85" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="B85" s="49" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="C85" s="35" t="s">
         <v>27</v>
@@ -23625,10 +23625,10 @@
     </row>
     <row r="86" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="B86" s="49" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="C86" s="35" t="s">
         <v>27</v>
@@ -23642,10 +23642,10 @@
     </row>
     <row r="87" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="B87" s="49" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="C87" s="35" t="s">
         <v>27</v>
@@ -23659,10 +23659,10 @@
     </row>
     <row r="88" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B88" s="49" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="C88" s="35" t="s">
         <v>27</v>
@@ -23676,10 +23676,10 @@
     </row>
     <row r="89" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="B89" s="49" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="C89" s="35" t="s">
         <v>27</v>
@@ -23693,10 +23693,10 @@
     </row>
     <row r="90" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="B90" s="49" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="C90" s="35" t="s">
         <v>27</v>
@@ -23710,10 +23710,10 @@
     </row>
     <row r="91" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="B91" s="49" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="C91" s="35" t="s">
         <v>27</v>
@@ -23727,10 +23727,10 @@
     </row>
     <row r="92" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="B92" s="49" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="C92" s="35" t="s">
         <v>27</v>
@@ -23744,10 +23744,10 @@
     </row>
     <row r="93" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="B93" s="49" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="C93" s="35" t="s">
         <v>27</v>
@@ -23761,10 +23761,10 @@
     </row>
     <row r="94" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="B94" s="49" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="C94" s="35" t="s">
         <v>27</v>
@@ -23778,10 +23778,10 @@
     </row>
     <row r="95" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="B95" s="49" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="C95" s="35" t="s">
         <v>27</v>
@@ -26259,10 +26259,10 @@
     </row>
     <row r="102" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A102" s="18" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="B102" s="47" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>27</v>
@@ -26300,10 +26300,10 @@
     </row>
     <row r="103" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A103" s="18" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="B103" s="47" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="C103" s="14" t="s">
         <v>27</v>
@@ -26320,10 +26320,10 @@
     </row>
     <row r="104" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A104" s="18" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="B104" s="47" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="C104" s="14" t="s">
         <v>27</v>
@@ -26337,10 +26337,10 @@
     </row>
     <row r="105" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" s="18" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="B105" s="47" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="C105" s="14" t="s">
         <v>27</v>
@@ -26354,10 +26354,10 @@
     </row>
     <row r="106" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" s="18" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="B106" s="47" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="C106" s="14" t="s">
         <v>27</v>
@@ -26371,10 +26371,10 @@
     </row>
     <row r="107" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A107" s="18" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="B107" s="47" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="C107" s="14" t="s">
         <v>27</v>
@@ -26388,10 +26388,10 @@
     </row>
     <row r="108" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A108" s="18" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="B108" s="47" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>27</v>
@@ -26405,10 +26405,10 @@
     </row>
     <row r="109" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A109" s="18" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="B109" s="47" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>27</v>
@@ -26422,7 +26422,7 @@
     </row>
     <row r="110" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="18" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="B110" s="48" t="s">
         <v>1804</v>
@@ -26445,13 +26445,13 @@
         <v>Users</v>
       </c>
       <c r="L110" s="18" t="s">
+        <v>3335</v>
+      </c>
+      <c r="M110" s="20" t="s">
+        <v>3337</v>
+      </c>
+      <c r="N110" s="20" t="s">
         <v>3336</v>
-      </c>
-      <c r="M110" s="20" t="s">
-        <v>3338</v>
-      </c>
-      <c r="N110" s="20" t="s">
-        <v>3337</v>
       </c>
       <c r="P110" s="24" t="s">
         <v>874</v>
@@ -26462,7 +26462,7 @@
     </row>
     <row r="111" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" s="18" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="B111" s="48" t="s">
         <v>1805</v>
@@ -26479,10 +26479,10 @@
     </row>
     <row r="112" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A112" s="18" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="B112" s="48" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="C112" s="14" t="s">
         <v>27</v>
@@ -26496,10 +26496,10 @@
     </row>
     <row r="113" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="18" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="B113" s="48" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>27</v>
@@ -26513,10 +26513,10 @@
     </row>
     <row r="114" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" s="18" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="B114" s="48" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="C114" s="14" t="s">
         <v>27</v>
@@ -26530,10 +26530,10 @@
     </row>
     <row r="115" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A115" s="18" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="C115" s="14" t="s">
         <v>27</v>
@@ -26547,10 +26547,10 @@
     </row>
     <row r="116" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="18" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="B116" s="48" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="C116" s="14" t="s">
         <v>27</v>
@@ -26564,10 +26564,10 @@
     </row>
     <row r="117" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A117" s="18" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="B117" s="48" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="C117" s="14" t="s">
         <v>27</v>
@@ -26581,10 +26581,10 @@
     </row>
     <row r="118" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A118" s="18" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="B118" s="48" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="C118" s="14" t="s">
         <v>27</v>
@@ -26598,10 +26598,10 @@
     </row>
     <row r="119" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A119" s="18" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="B119" s="48" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="C119" s="14" t="s">
         <v>27</v>
@@ -26615,10 +26615,10 @@
     </row>
     <row r="120" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="18" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="B120" s="49" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="C120" s="14" t="s">
         <v>27</v>
@@ -26632,10 +26632,10 @@
     </row>
     <row r="121" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A121" s="18" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="B121" s="49" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="C121" s="14" t="s">
         <v>27</v>
@@ -26649,10 +26649,10 @@
     </row>
     <row r="122" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="18" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="B122" s="49" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="C122" s="14" t="s">
         <v>27</v>
@@ -26666,10 +26666,10 @@
     </row>
     <row r="123" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A123" s="18" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B123" s="49" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="C123" s="14" t="s">
         <v>27</v>
@@ -26683,10 +26683,10 @@
     </row>
     <row r="124" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="18" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="B124" s="49" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="C124" s="14" t="s">
         <v>27</v>
@@ -26700,7 +26700,7 @@
     </row>
     <row r="125" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="18" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="B125" s="49" t="s">
         <v>1816</v>
@@ -26717,7 +26717,7 @@
     </row>
     <row r="126" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="18" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="B126" s="49" t="s">
         <v>1795</v>
@@ -26734,7 +26734,7 @@
     </row>
     <row r="127" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="18" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B127" s="49" t="s">
         <v>1924</v>
@@ -26751,10 +26751,10 @@
     </row>
     <row r="128" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A128" s="18" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="B128" s="49" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="C128" s="14" t="s">
         <v>27</v>
@@ -26768,7 +26768,7 @@
     </row>
     <row r="129" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="18" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="B129" s="49" t="s">
         <v>2024</v>
@@ -26785,7 +26785,7 @@
     </row>
     <row r="130" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="18" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="B130" s="49" t="s">
         <v>1784</v>
@@ -26802,7 +26802,7 @@
     </row>
     <row r="131" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A131" s="18" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="B131" s="49" t="s">
         <v>1785</v>
@@ -26819,7 +26819,7 @@
     </row>
     <row r="132" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="18" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="B132" s="49" t="s">
         <v>1786</v>
@@ -26836,7 +26836,7 @@
     </row>
     <row r="133" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A133" s="18" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="B133" s="49" t="s">
         <v>1787</v>
@@ -26853,10 +26853,10 @@
     </row>
     <row r="134" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="18" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="B134" s="49" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C134" s="14" t="s">
         <v>27</v>
@@ -26870,10 +26870,10 @@
     </row>
     <row r="135" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="18" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="B135" s="49" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="C135" s="14" t="s">
         <v>27</v>
@@ -26887,10 +26887,10 @@
     </row>
     <row r="136" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="18" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="B136" s="49" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="C136" s="14" t="s">
         <v>27</v>
@@ -26904,10 +26904,10 @@
     </row>
     <row r="137" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="18" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="B137" s="49" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="C137" s="14" t="s">
         <v>27</v>
@@ -26921,10 +26921,10 @@
     </row>
     <row r="138" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="18" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="B138" s="49" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C138" s="14" t="s">
         <v>27</v>
@@ -26938,7 +26938,7 @@
     </row>
     <row r="139" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="18" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B139" s="49" t="s">
         <v>1795</v>
@@ -26955,7 +26955,7 @@
     </row>
     <row r="140" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="18" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="B140" s="49" t="s">
         <v>1924</v>
@@ -26972,10 +26972,10 @@
     </row>
     <row r="141" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A141" s="18" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B141" s="49" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="C141" s="14" t="s">
         <v>27</v>
@@ -26989,10 +26989,10 @@
     </row>
     <row r="142" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A142" s="18" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B142" s="49" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="C142" s="14" t="s">
         <v>27</v>
@@ -27006,10 +27006,10 @@
     </row>
     <row r="143" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A143" s="18" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="B143" s="49" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="C143" s="14" t="s">
         <v>27</v>
@@ -27023,10 +27023,10 @@
     </row>
     <row r="144" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="18" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="B144" s="49" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>27</v>
@@ -27040,7 +27040,7 @@
     </row>
     <row r="145" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="18" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="B145" s="49" t="s">
         <v>2517</v>
@@ -27057,7 +27057,7 @@
     </row>
     <row r="146" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="18" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B146" s="49" t="s">
         <v>2139</v>
@@ -27074,7 +27074,7 @@
     </row>
     <row r="147" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A147" s="18" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="B147" s="49" t="s">
         <v>2035</v>
@@ -27094,7 +27094,7 @@
     </row>
     <row r="148" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A148" s="18" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="B148" s="49" t="s">
         <v>2036</v>
@@ -27114,7 +27114,7 @@
     </row>
     <row r="149" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A149" s="18" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="B149" s="49" t="s">
         <v>2037</v>
@@ -27134,10 +27134,10 @@
     </row>
     <row r="150" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="18" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="B150" s="49" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="C150" s="14" t="s">
         <v>27</v>
@@ -27151,10 +27151,10 @@
     </row>
     <row r="151" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="18" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="B151" s="49" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="C151" s="14" t="s">
         <v>27</v>
@@ -27168,10 +27168,10 @@
     </row>
     <row r="152" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="18" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="B152" s="49" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C152" s="14" t="s">
         <v>27</v>
@@ -27185,10 +27185,10 @@
     </row>
     <row r="153" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="18" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="B153" s="49" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="C153" s="14" t="s">
         <v>27</v>
@@ -27202,7 +27202,7 @@
     </row>
     <row r="154" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A154" s="18" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="B154" s="49" t="s">
         <v>2042</v>
@@ -27219,7 +27219,7 @@
     </row>
     <row r="155" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A155" s="18" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="B155" s="49" t="s">
         <v>2043</v>
@@ -27236,7 +27236,7 @@
     </row>
     <row r="156" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A156" s="18" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="B156" s="49" t="s">
         <v>2044</v>
@@ -27253,10 +27253,10 @@
     </row>
     <row r="157" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A157" s="18" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="B157" s="49" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="C157" s="14" t="s">
         <v>27</v>
@@ -27270,10 +27270,10 @@
     </row>
     <row r="158" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" s="18" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="B158" s="49" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="C158" s="14" t="s">
         <v>27</v>
@@ -27287,10 +27287,10 @@
     </row>
     <row r="159" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A159" s="18" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="B159" s="49" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="C159" s="14" t="s">
         <v>27</v>
@@ -27304,10 +27304,10 @@
     </row>
     <row r="160" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A160" s="18" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B160" s="49" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="C160" s="14" t="s">
         <v>27</v>
@@ -27321,10 +27321,10 @@
     </row>
     <row r="161" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A161" s="18" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B161" s="49" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>27</v>
@@ -27338,10 +27338,10 @@
     </row>
     <row r="162" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="18" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B162" s="49" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C162" s="14" t="s">
         <v>27</v>
@@ -27355,10 +27355,10 @@
     </row>
     <row r="163" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A163" s="18" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B163" s="49" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="C163" s="14" t="s">
         <v>27</v>
@@ -27372,10 +27372,10 @@
     </row>
     <row r="164" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A164" s="18" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B164" s="49" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="C164" s="14" t="s">
         <v>27</v>
@@ -27389,10 +27389,10 @@
     </row>
     <row r="165" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A165" s="18" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="B165" s="49" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="C165" s="14" t="s">
         <v>27</v>
@@ -27406,10 +27406,10 @@
     </row>
     <row r="166" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A166" s="18" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="B166" s="49" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="C166" s="14" t="s">
         <v>27</v>
@@ -27423,10 +27423,10 @@
     </row>
     <row r="167" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A167" s="18" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="B167" s="49" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="C167" s="14" t="s">
         <v>27</v>
@@ -27440,10 +27440,10 @@
     </row>
     <row r="168" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A168" s="18" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="B168" s="49" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C168" s="14" t="s">
         <v>27</v>
@@ -27457,10 +27457,10 @@
     </row>
     <row r="169" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A169" s="18" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="B169" s="49" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="C169" s="14" t="s">
         <v>27</v>
@@ -27474,10 +27474,10 @@
     </row>
     <row r="170" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A170" s="18" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B170" s="49" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="C170" s="14" t="s">
         <v>27</v>
@@ -27491,10 +27491,10 @@
     </row>
     <row r="171" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A171" s="18" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="B171" s="49" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="C171" s="14" t="s">
         <v>27</v>
@@ -27508,10 +27508,10 @@
     </row>
     <row r="172" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A172" s="18" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="B172" s="49" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="C172" s="14" t="s">
         <v>27</v>
@@ -27525,7 +27525,7 @@
     </row>
     <row r="173" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A173" s="18" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="B173" s="49" t="s">
         <v>2056</v>
@@ -27542,7 +27542,7 @@
     </row>
     <row r="174" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A174" s="18" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="B174" s="49" t="s">
         <v>1827</v>
@@ -27559,7 +27559,7 @@
     </row>
     <row r="175" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A175" s="18" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="B175" s="49" t="s">
         <v>1828</v>
@@ -27576,7 +27576,7 @@
     </row>
     <row r="176" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A176" s="18" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B176" s="49" t="s">
         <v>1829</v>
@@ -27593,7 +27593,7 @@
     </row>
     <row r="177" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A177" s="18" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B177" s="49" t="s">
         <v>2060</v>
@@ -27610,7 +27610,7 @@
     </row>
     <row r="178" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="18" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B178" s="49" t="s">
         <v>2156</v>
@@ -27627,7 +27627,7 @@
     </row>
     <row r="179" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A179" s="18" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B179" s="49" t="s">
         <v>1827</v>
@@ -27644,7 +27644,7 @@
     </row>
     <row r="180" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="18" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B180" s="49" t="s">
         <v>1828</v>
@@ -27661,7 +27661,7 @@
     </row>
     <row r="181" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A181" s="18" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="B181" s="49" t="s">
         <v>1829</v>
@@ -27678,7 +27678,7 @@
     </row>
     <row r="182" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A182" s="18" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="B182" s="49" t="s">
         <v>2060</v>
@@ -27695,7 +27695,7 @@
     </row>
     <row r="183" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A183" s="18" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="B183" s="49" t="s">
         <v>2156</v>
@@ -27712,7 +27712,7 @@
     </row>
     <row r="184" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A184" s="18" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="B184" s="49" t="s">
         <v>2012</v>
@@ -27729,7 +27729,7 @@
     </row>
     <row r="185" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A185" s="18" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="B185" s="49" t="s">
         <v>2013</v>
@@ -27746,10 +27746,10 @@
     </row>
     <row r="186" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A186" s="18" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="B186" s="48" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="C186" s="14" t="s">
         <v>27</v>
@@ -27763,7 +27763,7 @@
     </row>
     <row r="187" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A187" s="18" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="B187" s="48" t="s">
         <v>1832</v>
@@ -27780,7 +27780,7 @@
     </row>
     <row r="188" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="18" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="B188" s="49" t="s">
         <v>2061</v>
@@ -27797,7 +27797,7 @@
     </row>
     <row r="189" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A189" s="18" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="B189" s="49" t="s">
         <v>2062</v>
@@ -28338,11 +28338,11 @@
       </c>
       <c r="J19" s="8" t="str">
         <f ca="1">"RepositoriesName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>RepositoriesName12082024163244</v>
+        <v>RepositoriesName12082024222959</v>
       </c>
       <c r="K19" s="8" t="str">
         <f ca="1">"docker://wftedgeregistryprdcr.azurecr.io"&amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>docker://wftedgeregistryprdcr.azurecr.io12082024163244</v>
+        <v>docker://wftedgeregistryprdcr.azurecr.io12082024222959</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>1122</v>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="N26" s="8" t="str">
         <f ca="1">"UserName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>UserName12082024163244</v>
+        <v>UserName12082024222959</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
@@ -28846,10 +28846,10 @@
     </row>
     <row r="47" spans="1:22" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="115" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="B47" s="47" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>27</v>
@@ -28863,10 +28863,10 @@
     </row>
     <row r="48" spans="1:22" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="115" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="B48" s="47" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>27</v>
@@ -28880,10 +28880,10 @@
     </row>
     <row r="49" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="115" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="B49" s="47" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>27</v>
@@ -28900,10 +28900,10 @@
     </row>
     <row r="50" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="115" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="B50" s="47" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>27</v>
@@ -28917,10 +28917,10 @@
     </row>
     <row r="51" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="115" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="B51" s="47" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>27</v>
@@ -28934,7 +28934,7 @@
     </row>
     <row r="52" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="115" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B52" s="48" t="s">
         <v>1804</v>
@@ -28951,7 +28951,7 @@
     </row>
     <row r="53" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="115" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="B53" s="48" t="s">
         <v>1805</v>
@@ -28968,10 +28968,10 @@
     </row>
     <row r="54" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="115" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B54" s="48" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>27</v>
@@ -28985,10 +28985,10 @@
     </row>
     <row r="55" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="115" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="B55" s="48" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>27</v>
@@ -29002,10 +29002,10 @@
     </row>
     <row r="56" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="115" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="B56" s="48" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>27</v>
@@ -29019,10 +29019,10 @@
     </row>
     <row r="57" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="115" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>27</v>
@@ -29036,10 +29036,10 @@
     </row>
     <row r="58" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="115" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>27</v>
@@ -29053,10 +29053,10 @@
     </row>
     <row r="59" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="115" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>27</v>
@@ -29070,7 +29070,7 @@
     </row>
     <row r="60" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="115" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="B60" s="49" t="s">
         <v>2509</v>
@@ -29087,7 +29087,7 @@
     </row>
     <row r="61" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="115" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="B61" s="49" t="s">
         <v>1816</v>
@@ -29104,7 +29104,7 @@
     </row>
     <row r="62" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="115" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="B62" s="49" t="s">
         <v>1795</v>
@@ -29121,7 +29121,7 @@
     </row>
     <row r="63" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="115" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="B63" s="49" t="s">
         <v>1924</v>
@@ -29138,10 +29138,10 @@
     </row>
     <row r="64" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="115" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>27</v>
@@ -29155,7 +29155,7 @@
     </row>
     <row r="65" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="115" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="B65" s="49" t="s">
         <v>2024</v>
@@ -29172,7 +29172,7 @@
     </row>
     <row r="66" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="115" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B66" s="49" t="s">
         <v>1784</v>
@@ -29189,7 +29189,7 @@
     </row>
     <row r="67" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="115" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="B67" s="49" t="s">
         <v>1785</v>
@@ -29206,7 +29206,7 @@
     </row>
     <row r="68" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="115" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="B68" s="49" t="s">
         <v>1786</v>
@@ -29223,7 +29223,7 @@
     </row>
     <row r="69" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="115" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="B69" s="49" t="s">
         <v>1787</v>
@@ -29240,10 +29240,10 @@
     </row>
     <row r="70" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="115" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B70" s="49" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="C70" s="14" t="s">
         <v>27</v>
@@ -29257,10 +29257,10 @@
     </row>
     <row r="71" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="115" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B71" s="49" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>27</v>
@@ -29274,10 +29274,10 @@
     </row>
     <row r="72" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="115" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="B72" s="49" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="C72" s="14" t="s">
         <v>27</v>
@@ -29291,10 +29291,10 @@
     </row>
     <row r="73" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="115" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="B73" s="49" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>27</v>
@@ -29308,7 +29308,7 @@
     </row>
     <row r="74" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="115" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="B74" s="49" t="s">
         <v>1795</v>
@@ -29325,7 +29325,7 @@
     </row>
     <row r="75" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="115" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="B75" s="49" t="s">
         <v>1924</v>
@@ -29342,10 +29342,10 @@
     </row>
     <row r="76" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="115" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="B76" s="49" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="C76" s="14" t="s">
         <v>27</v>
@@ -29359,10 +29359,10 @@
     </row>
     <row r="77" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="115" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="B77" s="49" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C77" s="14" t="s">
         <v>27</v>
@@ -29376,10 +29376,10 @@
     </row>
     <row r="78" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="115" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="B78" s="49" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="C78" s="14" t="s">
         <v>27</v>
@@ -29393,7 +29393,7 @@
     </row>
     <row r="79" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="115" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="B79" s="49" t="s">
         <v>2517</v>
@@ -29410,7 +29410,7 @@
     </row>
     <row r="80" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="115" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="B80" s="49" t="s">
         <v>2155</v>
@@ -29430,7 +29430,7 @@
     </row>
     <row r="81" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="115" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="B81" s="49" t="s">
         <v>2035</v>
@@ -29450,7 +29450,7 @@
     </row>
     <row r="82" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="115" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="B82" s="49" t="s">
         <v>2036</v>
@@ -29470,7 +29470,7 @@
     </row>
     <row r="83" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="115" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="B83" s="49" t="s">
         <v>2037</v>
@@ -29490,10 +29490,10 @@
     </row>
     <row r="84" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="115" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B84" s="49" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>27</v>
@@ -29507,10 +29507,10 @@
     </row>
     <row r="85" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="115" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="B85" s="49" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>27</v>
@@ -29524,10 +29524,10 @@
     </row>
     <row r="86" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="115" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="B86" s="49" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>27</v>
@@ -29541,7 +29541,7 @@
     </row>
     <row r="87" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="115" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B87" s="49" t="s">
         <v>2042</v>
@@ -29558,7 +29558,7 @@
     </row>
     <row r="88" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="115" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="B88" s="49" t="s">
         <v>2043</v>
@@ -29575,7 +29575,7 @@
     </row>
     <row r="89" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="115" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B89" s="49" t="s">
         <v>2044</v>
@@ -29592,10 +29592,10 @@
     </row>
     <row r="90" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="115" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="B90" s="49" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>27</v>
@@ -29609,10 +29609,10 @@
     </row>
     <row r="91" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="115" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B91" s="49" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>27</v>
@@ -29626,10 +29626,10 @@
     </row>
     <row r="92" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="115" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B92" s="49" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>27</v>
@@ -29643,10 +29643,10 @@
     </row>
     <row r="93" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="115" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B93" s="49" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>27</v>
@@ -29660,10 +29660,10 @@
     </row>
     <row r="94" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="115" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B94" s="49" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>27</v>
@@ -29677,10 +29677,10 @@
     </row>
     <row r="95" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="115" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B95" s="49" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>27</v>
@@ -29694,10 +29694,10 @@
     </row>
     <row r="96" spans="1:9" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="115" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B96" s="49" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>27</v>
@@ -29711,10 +29711,10 @@
     </row>
     <row r="97" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="115" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="B97" s="49" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>27</v>
@@ -29728,10 +29728,10 @@
     </row>
     <row r="98" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="115" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B98" s="49" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>27</v>
@@ -29745,10 +29745,10 @@
     </row>
     <row r="99" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="115" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B99" s="49" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C99" s="14" t="s">
         <v>27</v>
@@ -29762,10 +29762,10 @@
     </row>
     <row r="100" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="115" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="B100" s="49" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C100" s="14" t="s">
         <v>27</v>
@@ -29779,10 +29779,10 @@
     </row>
     <row r="101" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="115" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="B101" s="49" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>27</v>
@@ -29796,7 +29796,7 @@
     </row>
     <row r="102" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="115" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="B102" s="49" t="s">
         <v>2056</v>
@@ -29813,7 +29813,7 @@
     </row>
     <row r="103" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="115" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B103" s="49" t="s">
         <v>1827</v>
@@ -29830,7 +29830,7 @@
     </row>
     <row r="104" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="115" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B104" s="49" t="s">
         <v>1828</v>
@@ -29847,7 +29847,7 @@
     </row>
     <row r="105" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="115" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="B105" s="49" t="s">
         <v>1829</v>
@@ -29864,7 +29864,7 @@
     </row>
     <row r="106" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="115" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="B106" s="49" t="s">
         <v>2060</v>
@@ -29881,7 +29881,7 @@
     </row>
     <row r="107" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="115" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B107" s="49" t="s">
         <v>2156</v>
@@ -29898,7 +29898,7 @@
     </row>
     <row r="108" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="115" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="B108" s="49" t="s">
         <v>1827</v>
@@ -29915,7 +29915,7 @@
     </row>
     <row r="109" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="115" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="B109" s="49" t="s">
         <v>1828</v>
@@ -29932,7 +29932,7 @@
     </row>
     <row r="110" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="115" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B110" s="49" t="s">
         <v>1829</v>
@@ -29949,7 +29949,7 @@
     </row>
     <row r="111" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="115" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="B111" s="49" t="s">
         <v>2060</v>
@@ -29966,7 +29966,7 @@
     </row>
     <row r="112" spans="1:5" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="115" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B112" s="49" t="s">
         <v>2156</v>
@@ -29983,10 +29983,10 @@
     </row>
     <row r="113" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="115" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="B113" s="49" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>27</v>
@@ -30000,7 +30000,7 @@
     </row>
     <row r="114" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="115" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B114" s="49" t="s">
         <v>2013</v>
@@ -30017,10 +30017,10 @@
     </row>
     <row r="115" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="115" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="C115" s="14" t="s">
         <v>27</v>
@@ -30037,7 +30037,7 @@
     </row>
     <row r="116" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="115" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="B116" s="48" t="s">
         <v>1832</v>
@@ -30057,7 +30057,7 @@
     </row>
     <row r="117" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="115" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="B117" s="49" t="s">
         <v>2061</v>
@@ -30074,7 +30074,7 @@
     </row>
     <row r="118" spans="1:10" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="115" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="B118" s="49" t="s">
         <v>2062</v>
@@ -30250,7 +30250,7 @@
       </c>
       <c r="G5" s="40" t="str">
         <f ca="1">"UserGroup" &amp; TEXT(NOW(),"yyyyMMddhhmmss")</f>
-        <v>UserGroup20240812163244</v>
+        <v>UserGroup20240812222959</v>
       </c>
       <c r="L5" s="69"/>
     </row>
@@ -30316,7 +30316,7 @@
         <v>2473</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="L8" s="69"/>
     </row>
@@ -31877,13 +31877,13 @@
         <v>1992</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="S1" s="16" t="s">
+        <v>2836</v>
+      </c>
+      <c r="T1" s="16" t="s">
         <v>2837</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>2838</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="103" customFormat="1" ht="26" x14ac:dyDescent="0.35">
@@ -32346,7 +32346,7 @@
         <v>2473</v>
       </c>
       <c r="P24" s="106" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="105" customFormat="1" x14ac:dyDescent="0.35">
@@ -32402,7 +32402,7 @@
     </row>
     <row r="28" spans="1:16" s="105" customFormat="1" ht="39" x14ac:dyDescent="0.35">
       <c r="A28" s="104" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="B28" s="104" t="s">
         <v>831</v>
@@ -32419,7 +32419,7 @@
     </row>
     <row r="29" spans="1:16" s="105" customFormat="1" ht="39" x14ac:dyDescent="0.35">
       <c r="A29" s="104" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="B29" s="104" t="s">
         <v>835</v>
@@ -32436,7 +32436,7 @@
     </row>
     <row r="30" spans="1:16" s="105" customFormat="1" ht="39" x14ac:dyDescent="0.35">
       <c r="A30" s="104" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="B30" s="104" t="s">
         <v>838</v>
@@ -32453,7 +32453,7 @@
     </row>
     <row r="31" spans="1:16" s="105" customFormat="1" ht="52" x14ac:dyDescent="0.35">
       <c r="A31" s="104" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="B31" s="104" t="s">
         <v>815</v>
@@ -32470,7 +32470,7 @@
     </row>
     <row r="32" spans="1:16" s="105" customFormat="1" ht="52" x14ac:dyDescent="0.35">
       <c r="A32" s="104" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="B32" s="104" t="s">
         <v>850</v>
@@ -32487,7 +32487,7 @@
     </row>
     <row r="33" spans="1:5" s="105" customFormat="1" ht="65" x14ac:dyDescent="0.35">
       <c r="A33" s="104" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="B33" s="104" t="s">
         <v>816</v>
@@ -32504,7 +32504,7 @@
     </row>
     <row r="34" spans="1:5" s="105" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="104" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="B34" s="104" t="s">
         <v>851</v>
@@ -32555,7 +32555,7 @@
     </row>
     <row r="37" spans="1:5" s="105" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="104" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="B37" s="104" t="s">
         <v>1777</v>
@@ -32572,7 +32572,7 @@
     </row>
     <row r="38" spans="1:5" s="105" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="104" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="B38" s="108" t="s">
         <v>832</v>
@@ -32589,7 +32589,7 @@
     </row>
     <row r="39" spans="1:5" s="105" customFormat="1" ht="52" x14ac:dyDescent="0.35">
       <c r="A39" s="104" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="B39" s="108" t="s">
         <v>836</v>
@@ -32606,7 +32606,7 @@
     </row>
     <row r="40" spans="1:5" s="105" customFormat="1" ht="39" x14ac:dyDescent="0.35">
       <c r="A40" s="104" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="B40" s="108" t="s">
         <v>839</v>
@@ -32623,7 +32623,7 @@
     </row>
     <row r="41" spans="1:5" s="105" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="104" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="B41" s="104" t="s">
         <v>852</v>
@@ -32640,7 +32640,7 @@
     </row>
     <row r="42" spans="1:5" s="105" customFormat="1" ht="38" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="104" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
       <c r="B42" s="104" t="s">
         <v>853</v>
@@ -32657,7 +32657,7 @@
     </row>
     <row r="43" spans="1:5" s="105" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="104" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="B43" s="108" t="s">
         <v>854</v>
@@ -32691,7 +32691,7 @@
     </row>
     <row r="45" spans="1:5" s="105" customFormat="1" ht="26" x14ac:dyDescent="0.35">
       <c r="A45" s="104" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="B45" s="108" t="s">
         <v>821</v>
@@ -32708,7 +32708,7 @@
     </row>
     <row r="46" spans="1:5" s="105" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="104" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="B46" s="104" t="s">
         <v>1777</v>
@@ -32725,7 +32725,7 @@
     </row>
     <row r="47" spans="1:5" s="105" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="104" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="B47" s="104" t="s">
         <v>1777</v>
@@ -32762,7 +32762,7 @@
         <v>455</v>
       </c>
       <c r="B49" s="104" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>27</v>
@@ -32776,7 +32776,7 @@
     </row>
     <row r="50" spans="1:5" s="105" customFormat="1" ht="91" x14ac:dyDescent="0.35">
       <c r="A50" s="111" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="B50" s="108" t="s">
         <v>855</v>
@@ -32793,7 +32793,7 @@
     </row>
     <row r="51" spans="1:5" s="105" customFormat="1" ht="78" x14ac:dyDescent="0.35">
       <c r="A51" s="111" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="B51" s="108" t="s">
         <v>856</v>
@@ -32810,7 +32810,7 @@
     </row>
     <row r="52" spans="1:5" s="105" customFormat="1" ht="78" x14ac:dyDescent="0.35">
       <c r="A52" s="111" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="B52" s="108" t="s">
         <v>857</v>
@@ -32827,7 +32827,7 @@
     </row>
     <row r="53" spans="1:5" s="105" customFormat="1" ht="78" x14ac:dyDescent="0.35">
       <c r="A53" s="111" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="B53" s="108" t="s">
         <v>858</v>
@@ -32878,7 +32878,7 @@
     </row>
     <row r="56" spans="1:5" s="105" customFormat="1" ht="39" x14ac:dyDescent="0.35">
       <c r="A56" s="111" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="B56" s="108" t="s">
         <v>859</v>
@@ -32912,7 +32912,7 @@
     </row>
     <row r="58" spans="1:5" s="105" customFormat="1" ht="104" x14ac:dyDescent="0.35">
       <c r="A58" s="111" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="B58" s="108" t="s">
         <v>834</v>
@@ -32929,7 +32929,7 @@
     </row>
     <row r="59" spans="1:5" s="105" customFormat="1" ht="104" x14ac:dyDescent="0.35">
       <c r="A59" s="111" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="B59" s="108" t="s">
         <v>837</v>
@@ -32946,7 +32946,7 @@
     </row>
     <row r="60" spans="1:5" s="105" customFormat="1" ht="91" x14ac:dyDescent="0.35">
       <c r="A60" s="111" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="B60" s="108" t="s">
         <v>840</v>
@@ -32963,7 +32963,7 @@
     </row>
     <row r="61" spans="1:5" s="105" customFormat="1" ht="91" x14ac:dyDescent="0.35">
       <c r="A61" s="111" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="B61" s="108" t="s">
         <v>828</v>
@@ -32980,7 +32980,7 @@
     </row>
     <row r="62" spans="1:5" s="105" customFormat="1" ht="117" x14ac:dyDescent="0.35">
       <c r="A62" s="111" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="B62" s="108" t="s">
         <v>860</v>
@@ -32997,7 +32997,7 @@
     </row>
     <row r="63" spans="1:5" s="105" customFormat="1" ht="195" x14ac:dyDescent="0.35">
       <c r="A63" s="111" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="B63" s="108" t="s">
         <v>861</v>
@@ -33014,7 +33014,7 @@
     </row>
     <row r="64" spans="1:5" s="105" customFormat="1" ht="169" x14ac:dyDescent="0.35">
       <c r="A64" s="111" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="B64" s="108" t="s">
         <v>862</v>
@@ -33123,10 +33123,10 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" s="96" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="B69" s="108" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>27</v>
@@ -33140,10 +33140,10 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" s="96" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="B70" s="108" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="C70" s="14" t="s">
         <v>27</v>
@@ -33161,18 +33161,18 @@
         <v>2529</v>
       </c>
       <c r="J70" s="107" t="s">
+        <v>2807</v>
+      </c>
+      <c r="K70" s="107" t="s">
         <v>2808</v>
-      </c>
-      <c r="K70" s="107" t="s">
-        <v>2809</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" s="96" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="B71" s="108" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>27</v>
@@ -33190,18 +33190,18 @@
         <v>2529</v>
       </c>
       <c r="N71" s="107" t="s">
+        <v>2807</v>
+      </c>
+      <c r="O71" s="107" t="s">
         <v>2808</v>
-      </c>
-      <c r="O71" s="107" t="s">
-        <v>2809</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" s="96" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="B72" s="108" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="C72" s="14" t="s">
         <v>27</v>
@@ -33218,10 +33218,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" s="96" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="B73" s="108" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>27</v>
@@ -33238,7 +33238,7 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" s="96" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="B74" s="108" t="s">
         <v>2509</v>
@@ -33255,7 +33255,7 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" s="96" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="B75" s="108" t="s">
         <v>1795</v>
@@ -33272,10 +33272,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" s="96" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B76" s="108" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="C76" s="14" t="s">
         <v>27</v>
@@ -33289,7 +33289,7 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" s="96" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="B77" s="108" t="s">
         <v>1784</v>
@@ -33306,7 +33306,7 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" s="96" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="B78" s="108" t="s">
         <v>1785</v>
@@ -33323,7 +33323,7 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79" s="96" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="B79" s="108" t="s">
         <v>1786</v>
@@ -33340,7 +33340,7 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" s="96" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="B80" s="108" t="s">
         <v>1787</v>
@@ -33357,10 +33357,10 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" s="96" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="B81" s="108" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="C81" s="14" t="s">
         <v>27</v>
@@ -33374,10 +33374,10 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="96" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="B82" s="108" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>27</v>
@@ -33391,10 +33391,10 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" s="96" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="B83" s="108" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>27</v>
@@ -33408,10 +33408,10 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84" s="96" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="B84" s="108" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>27</v>
@@ -33425,10 +33425,10 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" s="96" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="B85" s="108" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>27</v>
@@ -33442,7 +33442,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86" s="96" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="B86" s="108" t="s">
         <v>2509</v>
@@ -33459,7 +33459,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" s="96" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="B87" s="108" t="s">
         <v>2155</v>
@@ -33477,7 +33477,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" s="96" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="B88" s="108" t="s">
         <v>2035</v>
@@ -33497,7 +33497,7 @@
     </row>
     <row r="89" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A89" s="96" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="B89" s="108" t="s">
         <v>2519</v>
@@ -33517,7 +33517,7 @@
     </row>
     <row r="90" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A90" s="96" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="B90" s="108" t="s">
         <v>2520</v>
@@ -33537,10 +33537,10 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" s="96" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="B91" s="104" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>27</v>
@@ -33554,10 +33554,10 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92" s="96" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="B92" s="108" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>27</v>
@@ -33571,10 +33571,10 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93" s="96" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="B93" s="108" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>27</v>
@@ -33588,10 +33588,10 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94" s="96" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="B94" s="108" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>27</v>
@@ -33605,10 +33605,10 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95" s="96" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="B95" s="108" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>27</v>
@@ -33622,7 +33622,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96" s="96" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="B96" s="108" t="s">
         <v>2042</v>
@@ -33639,10 +33639,10 @@
     </row>
     <row r="97" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A97" s="96" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="B97" s="108" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>27</v>
@@ -33656,10 +33656,10 @@
     </row>
     <row r="98" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A98" s="96" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="B98" s="108" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>27</v>
@@ -33673,10 +33673,10 @@
     </row>
     <row r="99" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A99" s="96" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="B99" s="108" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="C99" s="14" t="s">
         <v>27</v>
@@ -33690,10 +33690,10 @@
     </row>
     <row r="100" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A100" s="96" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="B100" s="108" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="C100" s="14" t="s">
         <v>27</v>
@@ -33707,10 +33707,10 @@
     </row>
     <row r="101" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A101" s="96" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="B101" s="108" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>27</v>
@@ -33724,10 +33724,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="96" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="B102" s="108" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>27</v>
@@ -33741,10 +33741,10 @@
     </row>
     <row r="103" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A103" s="96" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="B103" s="108" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="C103" s="14" t="s">
         <v>27</v>
@@ -33758,10 +33758,10 @@
     </row>
     <row r="104" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A104" s="96" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="B104" s="108" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="C104" s="14" t="s">
         <v>27</v>
@@ -33775,10 +33775,10 @@
     </row>
     <row r="105" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A105" s="96" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="B105" s="108" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="C105" s="14" t="s">
         <v>27</v>
@@ -33792,10 +33792,10 @@
     </row>
     <row r="106" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A106" s="96" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="B106" s="108" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="C106" s="14" t="s">
         <v>27</v>
@@ -33809,7 +33809,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="96" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="B107" s="108" t="s">
         <v>2056</v>
@@ -33826,10 +33826,10 @@
     </row>
     <row r="108" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A108" s="96" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="B108" s="108" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>27</v>
@@ -33843,10 +33843,10 @@
     </row>
     <row r="109" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A109" s="96" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="B109" s="108" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>27</v>
@@ -33860,10 +33860,10 @@
     </row>
     <row r="110" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A110" s="96" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="B110" s="108" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="C110" s="14" t="s">
         <v>27</v>
@@ -33877,10 +33877,10 @@
     </row>
     <row r="111" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A111" s="96" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="B111" s="108" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="C111" s="14" t="s">
         <v>27</v>
@@ -33894,10 +33894,10 @@
     </row>
     <row r="112" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A112" s="96" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="B112" s="108" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="C112" s="14" t="s">
         <v>27</v>
@@ -33911,10 +33911,10 @@
     </row>
     <row r="113" spans="1:20" ht="26" x14ac:dyDescent="0.35">
       <c r="A113" s="96" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="B113" s="108" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>27</v>
@@ -33928,10 +33928,10 @@
     </row>
     <row r="114" spans="1:20" ht="26" x14ac:dyDescent="0.35">
       <c r="A114" s="96" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="B114" s="108" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="C114" s="14" t="s">
         <v>27</v>
@@ -33945,10 +33945,10 @@
     </row>
     <row r="115" spans="1:20" ht="26" x14ac:dyDescent="0.35">
       <c r="A115" s="96" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B115" s="108" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="C115" s="14" t="s">
         <v>27</v>
@@ -33962,10 +33962,10 @@
     </row>
     <row r="116" spans="1:20" ht="26" x14ac:dyDescent="0.35">
       <c r="A116" s="96" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="B116" s="108" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="C116" s="14" t="s">
         <v>27</v>
@@ -33979,10 +33979,10 @@
     </row>
     <row r="117" spans="1:20" ht="26" x14ac:dyDescent="0.35">
       <c r="A117" s="96" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="B117" s="108" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="C117" s="14" t="s">
         <v>27</v>
@@ -33996,7 +33996,7 @@
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" s="96" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="B118" s="108" t="s">
         <v>2061</v>
@@ -34013,7 +34013,7 @@
     </row>
     <row r="119" spans="1:20" ht="26" x14ac:dyDescent="0.35">
       <c r="A119" s="96" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="B119" s="108" t="s">
         <v>2062</v>
@@ -34030,10 +34030,10 @@
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" s="96" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="B120" s="108" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="C120" s="14" t="s">
         <v>27</v>
@@ -34047,10 +34047,10 @@
     </row>
     <row r="121" spans="1:20" ht="39" x14ac:dyDescent="0.35">
       <c r="A121" s="96" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="B121" s="108" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="C121" s="14" t="s">
         <v>27</v>
@@ -34067,10 +34067,10 @@
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" s="96" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="B122" s="108" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="C122" s="14" t="s">
         <v>27</v>
@@ -34088,7 +34088,7 @@
         <v>2496</v>
       </c>
       <c r="T122" s="8" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.35">
@@ -34143,10 +34143,10 @@
         <v>26</v>
       </c>
       <c r="F1" s="54" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="H1" s="54"/>
       <c r="I1" s="54"/>
@@ -34283,7 +34283,7 @@
         <v>2473</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="61" customFormat="1" ht="26" x14ac:dyDescent="0.35">
@@ -34339,7 +34339,7 @@
     </row>
     <row r="12" spans="1:15" s="57" customFormat="1" ht="26" x14ac:dyDescent="0.35">
       <c r="A12" s="56" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B12" s="46" t="s">
         <v>2302</v>
@@ -34619,7 +34619,7 @@
     </row>
     <row r="26" spans="1:16" s="61" customFormat="1" ht="26" x14ac:dyDescent="0.35">
       <c r="A26" s="60" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="B26" s="60" t="s">
         <v>2316</v>
@@ -36329,11 +36329,11 @@
       </c>
       <c r="O43" s="1" t="str">
         <f ca="1">"Staging" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>Staging12082024163244</v>
+        <v>Staging12082024222959</v>
       </c>
       <c r="P43" s="1" t="str">
         <f ca="1">"EdgeDeviceStagingName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>EdgeDeviceStagingName12082024163244</v>
+        <v>EdgeDeviceStagingName12082024222959</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>2500</v>
@@ -37281,7 +37281,7 @@
       </c>
       <c r="AI81" s="86" t="str">
         <f ca="1">"WellName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>WellName12082024163244</v>
+        <v>WellName12082024222959</v>
       </c>
       <c r="AJ81" s="25" t="s">
         <v>559</v>
@@ -37433,11 +37433,11 @@
       </c>
       <c r="O89" s="1" t="str">
         <f ca="1">"Staging" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>Staging12082024163244</v>
+        <v>Staging12082024222959</v>
       </c>
       <c r="P89" s="1" t="str">
         <f ca="1">"EdgeDeviceStagingName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>EdgeDeviceStagingName12082024163244</v>
+        <v>EdgeDeviceStagingName12082024222959</v>
       </c>
       <c r="Q89" s="1"/>
       <c r="R89" s="1" t="s">
@@ -37489,11 +37489,11 @@
       </c>
       <c r="O90" s="1" t="str">
         <f ca="1">"Staging" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>Staging12082024163244</v>
+        <v>Staging12082024222959</v>
       </c>
       <c r="P90" s="1" t="str">
         <f ca="1">"EdgeDeviceStagingName" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>EdgeDeviceStagingName12082024163244</v>
+        <v>EdgeDeviceStagingName12082024222959</v>
       </c>
       <c r="Q90" s="1"/>
       <c r="R90" s="1" t="s">
@@ -38996,7 +38996,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9737375C-1F53-42FD-8F44-EC319193220E}">
-  <dimension ref="A1:AM143"/>
+  <dimension ref="A1:AM144"/>
   <sheetFormatPr defaultColWidth="57.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="85.453125" style="3" customWidth="1"/>
@@ -39128,13 +39128,13 @@
         <v>1780</v>
       </c>
       <c r="AJ1" s="16" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="AK1" s="16" t="s">
         <v>1300</v>
       </c>
       <c r="AL1" s="16" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="AM1" s="68" t="s">
         <v>1780</v>
@@ -39372,7 +39372,7 @@
         <v>2473</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -39394,7 +39394,7 @@
         <v>2473</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -39422,13 +39422,13 @@
         <v>2473</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="21"/>
       <c r="V13" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W13" s="10" t="s">
         <v>2495</v>
@@ -39715,7 +39715,7 @@
         <v>2473</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -39739,7 +39739,7 @@
         <v>2473</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -39763,7 +39763,7 @@
         <v>2473</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -39847,7 +39847,7 @@
         <v>2473</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G30" s="27" t="s">
         <v>582</v>
@@ -40140,7 +40140,7 @@
         <v>2473</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>868</v>
@@ -40175,7 +40175,7 @@
         <v>2473</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -40202,7 +40202,7 @@
         <v>2473</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
@@ -40232,7 +40232,7 @@
         <v>2473</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
@@ -40256,7 +40256,7 @@
         <v>2473</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -40280,7 +40280,7 @@
         <v>2473</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
@@ -40304,7 +40304,7 @@
         <v>2473</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="H48" s="3"/>
       <c r="N48" s="3"/>
@@ -40334,7 +40334,7 @@
         <v>2473</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
@@ -40369,7 +40369,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="V50" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W50" s="10" t="s">
         <v>2495</v>
@@ -40402,7 +40402,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="V51" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W51" s="10" t="s">
         <v>2495</v>
@@ -40435,7 +40435,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="V52" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W52" s="10" t="s">
         <v>2495</v>
@@ -40467,7 +40467,7 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="V53" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W53" s="10" t="s">
         <v>2495</v>
@@ -40499,7 +40499,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="V54" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W54" s="10" t="s">
         <v>2495</v>
@@ -40531,7 +40531,7 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="V55" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W55" s="10" t="s">
         <v>2495</v>
@@ -40563,7 +40563,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="V56" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W56" s="10" t="s">
         <v>2495</v>
@@ -40595,7 +40595,7 @@
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="V57" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W57" s="10" t="s">
         <v>2495</v>
@@ -40627,7 +40627,7 @@
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="V58" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W58" s="10" t="s">
         <v>2495</v>
@@ -40659,7 +40659,7 @@
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="V59" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W59" s="10" t="s">
         <v>2495</v>
@@ -40691,7 +40691,7 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="V60" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W60" s="10" t="s">
         <v>2495</v>
@@ -40723,7 +40723,7 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="V61" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W61" s="10" t="s">
         <v>2495</v>
@@ -40755,7 +40755,7 @@
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="V62" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W62" s="10" t="s">
         <v>2495</v>
@@ -40790,7 +40790,7 @@
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="V63" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="W63" s="10" t="s">
         <v>2495</v>
@@ -40822,7 +40822,7 @@
         <v>2473</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
@@ -40991,11 +40991,11 @@
       </c>
       <c r="N72" s="3" t="str">
         <f ca="1">"EdgeGroup" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>EdgeGroup12082024163244</v>
+        <v>EdgeGroup12082024222959</v>
       </c>
       <c r="O72" s="3" t="str">
         <f ca="1">"EdgeGroup" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>EdgeGroup12082024163244</v>
+        <v>EdgeGroup12082024222959</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>900</v>
@@ -41033,15 +41033,15 @@
         <v>2473</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="H73" s="3"/>
       <c r="N73" s="3" t="str">
         <f ca="1">"EdgeGroup" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>EdgeGroup12082024163244</v>
+        <v>EdgeGroup12082024222959</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="P73" s="3" t="s">
         <v>900</v>
@@ -41062,7 +41062,7 @@
         <v>8090</v>
       </c>
       <c r="AA73" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="74" spans="1:34" ht="29" x14ac:dyDescent="0.35">
@@ -41082,7 +41082,7 @@
         <v>2473</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="H74" s="3"/>
     </row>
@@ -41103,7 +41103,7 @@
         <v>2473</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="H75" s="3"/>
     </row>
@@ -41124,10 +41124,10 @@
         <v>2473</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="H76" s="3"/>
       <c r="J76" s="3"/>
@@ -41154,7 +41154,7 @@
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="str">
         <f ca="1">"EdgeGroup" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>EdgeGroup12082024163244</v>
+        <v>EdgeGroup12082024222959</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>867</v>
@@ -41200,7 +41200,7 @@
         <v>2473</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>899</v>
@@ -42418,16 +42418,16 @@
         <v>2473</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>2715</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="143" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
+        <v>3475</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>2716</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>2717</v>
-      </c>
       <c r="C143" s="3" t="s">
         <v>27</v>
       </c>
@@ -42438,7 +42438,7 @@
         <v>2473</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>1345</v>
+        <v>3474</v>
       </c>
       <c r="AA143" s="10" t="s">
         <v>1345</v>
@@ -42452,20 +42452,35 @@
       <c r="AD143" s="10">
         <v>8080</v>
       </c>
-      <c r="AE143" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="AH143" s="10" t="s">
-        <v>166</v>
-      </c>
+      <c r="AE143" s="27"/>
       <c r="AJ143" s="10" t="s">
+        <v>2718</v>
+      </c>
+      <c r="AK143" s="10" t="s">
         <v>2719</v>
-      </c>
-      <c r="AK143" s="10" t="s">
-        <v>2720</v>
       </c>
       <c r="AL143" s="10" t="s">
         <v>2495</v>
+      </c>
+    </row>
+    <row r="144" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A144" s="3" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D144" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E144" s="26" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>3474</v>
       </c>
     </row>
   </sheetData>
@@ -46681,11 +46696,11 @@
       <c r="I12" s="3"/>
       <c r="K12" s="35" t="str">
         <f t="shared" ref="K12:L16" ca="1" si="0">"AppGroup" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="L12" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="N12" s="69" t="s">
         <v>1782</v>
@@ -46713,11 +46728,11 @@
       <c r="I13" s="3"/>
       <c r="K13" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="L13" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="N13" s="69"/>
     </row>
@@ -46743,11 +46758,11 @@
       <c r="I14" s="3"/>
       <c r="K14" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="L14" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="N14" s="69"/>
     </row>
@@ -46773,11 +46788,11 @@
       <c r="I15" s="3"/>
       <c r="K15" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="L15" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="N15" s="69"/>
     </row>
@@ -46803,11 +46818,11 @@
       <c r="I16" s="3"/>
       <c r="K16" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="L16" s="35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="N16" s="69"/>
     </row>
@@ -47028,11 +47043,11 @@
       </c>
       <c r="K27" s="35" t="str">
         <f ca="1">"AppGroup" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="L27" s="35" t="str">
         <f ca="1">"AppGroup" &amp; TEXT(NOW(),"DDMMYYYhhmmss")</f>
-        <v>AppGroup12082024163244</v>
+        <v>AppGroup12082024222959</v>
       </c>
       <c r="N27" s="76"/>
     </row>
